--- a/Boils_per_Charge/Boils_per_Charge.xlsx
+++ b/Boils_per_Charge/Boils_per_Charge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3821" documentId="8_{E1B203CD-980D-4B68-9256-E22E05DA1089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6A8384E-D0DE-4AFB-B9A9-1290C76DCBED}"/>
+  <xr:revisionPtr revIDLastSave="4931" documentId="8_{E1B203CD-980D-4B68-9256-E22E05DA1089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16626B79-49DA-41E0-A4CD-9F3D9E60DCCB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
+    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -451,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>455544</v>
+        <v>599400</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -470,7 +470,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>56.717311658894097</v>
+        <v>42.669273817455</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -479,7 +479,7 @@
       </c>
       <c r="B6">
         <f>B3/(B4*B5)</f>
-        <v>5.3509882963305744</v>
+        <v>9.3588135385215008</v>
       </c>
     </row>
   </sheetData>

--- a/Boils_per_Charge/Boils_per_Charge.xlsx
+++ b/Boils_per_Charge/Boils_per_Charge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17144" documentId="8_{E1B203CD-980D-4B68-9256-E22E05DA1089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60E2B91F-5AD0-42E4-8E2F-4516EF2981FE}"/>
+  <xr:revisionPtr revIDLastSave="36803" documentId="8_{E1B203CD-980D-4B68-9256-E22E05DA1089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFFDBFEA-A638-4532-B523-C7562E12AE60}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
   </bookViews>
@@ -451,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>455544</v>
+        <v>1998000</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -462,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -470,7 +470,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>283.58911057349502</v>
+        <v>73.899900000000002</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -479,7 +479,7 @@
       </c>
       <c r="B6">
         <f>B3/(B4*B5)</f>
-        <v>1.0701880275738671</v>
+        <v>18.0243816297451</v>
       </c>
     </row>
   </sheetData>

--- a/Boils_per_Charge/Boils_per_Charge.xlsx
+++ b/Boils_per_Charge/Boils_per_Charge.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4151" documentId="8_{E1B203CD-980D-4B68-9256-E22E05DA1089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55316440-BFF7-44C1-98EF-CF816304F60F}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{873FD009-7918-4F29-ADAA-E07709D9B239}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
+    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -458,7 +458,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>1501</v>
+        <v>1576.05</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -466,7 +466,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>141.79316571261199</v>
+        <v>120.41892071952</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -475,7 +475,7 @@
       </c>
       <c r="B6">
         <f>B3/(B4*B5)</f>
-        <v>2.1403970308498534</v>
+        <v>2.4003004643540082</v>
       </c>
     </row>
   </sheetData>

--- a/Boils_per_Charge/Boils_per_Charge.xlsx
+++ b/Boils_per_Charge/Boils_per_Charge.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{873FD009-7918-4F29-ADAA-E07709D9B239}"/>
+  <xr:revisionPtr revIDLastSave="18891" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B6EAADB-9794-48F9-BA6E-507A98C60DA0}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -112,6 +112,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -447,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>455544</v>
+        <v>583906.56954386295</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -458,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>1576.05</v>
+        <v>1556.3679914586601</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -466,7 +470,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>120.41892071952</v>
+        <v>70.163978672883999</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -475,7 +479,7 @@
       </c>
       <c r="B6">
         <f>B3/(B4*B5)</f>
-        <v>2.4003004643540082</v>
+        <v>5.3470822333374901</v>
       </c>
     </row>
   </sheetData>

--- a/Boils_per_Charge/Boils_per_Charge.xlsx
+++ b/Boils_per_Charge/Boils_per_Charge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18891" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B6EAADB-9794-48F9-BA6E-507A98C60DA0}"/>
+  <xr:revisionPtr revIDLastSave="21201" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B345C1DC-C1B0-4576-B2F6-E9C5FDF4E08A}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
   </bookViews>
@@ -451,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>583906.56954386295</v>
+        <v>568920.11673045903</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -462,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>1556.3679914586601</v>
+        <v>1412.3931741036199</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -470,7 +470,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>70.163978672883999</v>
+        <v>72.009411860498702</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -479,7 +479,7 @@
       </c>
       <c r="B6">
         <f>B3/(B4*B5)</f>
-        <v>5.3470822333374901</v>
+        <v>5.5937933285562602</v>
       </c>
     </row>
   </sheetData>

--- a/Boils_per_Charge/Boils_per_Charge.xlsx
+++ b/Boils_per_Charge/Boils_per_Charge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21201" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B345C1DC-C1B0-4576-B2F6-E9C5FDF4E08A}"/>
+  <xr:revisionPtr revIDLastSave="21291" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9EF7E0F-AF96-4969-A35F-F52264E9311B}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
   </bookViews>
@@ -451,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>568920.11673045903</v>
+        <v>59084.818422765798</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -462,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>1412.3931741036199</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -470,7 +470,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>72.009411860498702</v>
+        <v>73.706326561884694</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -479,7 +479,7 @@
       </c>
       <c r="B6">
         <f>B3/(B4*B5)</f>
-        <v>5.5937933285562602</v>
+        <v>35.627768366612173</v>
       </c>
     </row>
   </sheetData>

--- a/Boils_per_Charge/Boils_per_Charge.xlsx
+++ b/Boils_per_Charge/Boils_per_Charge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21291" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9EF7E0F-AF96-4969-A35F-F52264E9311B}"/>
+  <xr:revisionPtr revIDLastSave="22260" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C12FA88E-5F40-448E-8BFE-8B215EDC5791}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
   </bookViews>
@@ -451,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>59084.818422765798</v>
+        <v>130738.255459668</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -470,7 +470,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>73.706326561884694</v>
+        <v>82.882171883409299</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -479,7 +479,7 @@
       </c>
       <c r="B6">
         <f>B3/(B4*B5)</f>
-        <v>35.627768366612173</v>
+        <v>70.106622443661109</v>
       </c>
     </row>
   </sheetData>

--- a/Boils_per_Charge/Boils_per_Charge.xlsx
+++ b/Boils_per_Charge/Boils_per_Charge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Boils_per_Charge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22260" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C12FA88E-5F40-448E-8BFE-8B215EDC5791}"/>
+  <xr:revisionPtr revIDLastSave="25260" documentId="121_{CCECF0A9-F738-47C2-A103-6D8479D23741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD7F3AE9-2A0F-4C26-8602-EB99BCFBFD0F}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{8DE6D8F7-A165-49AB-ACB4-90769F3729E6}"/>
   </bookViews>
@@ -451,7 +451,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>130738.255459668</v>
+        <v>63149.991064902199</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -462,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>22.5</v>
+        <v>1477.5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -470,7 +470,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>82.882171883409299</v>
+        <v>75.220639757313293</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -479,7 +479,7 @@
       </c>
       <c r="B6">
         <f>B3/(B4*B5)</f>
-        <v>70.106622443661109</v>
+        <v>0.56820988018345098</v>
       </c>
     </row>
   </sheetData>
